--- a/cet4/result/25_豪门甜宠_冰山总裁的契约娇妻/25_豪门甜宠_冰山总裁的契约娇妻_学习版.xlsx
+++ b/cet4/result/25_豪门甜宠_冰山总裁的契约娇妻/25_豪门甜宠_冰山总裁的契约娇妻_学习版.xlsx
@@ -397,591 +397,521 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D36"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>clerk</v>
       </c>
       <c r="B2" t="str">
-        <v>clerk</v>
+        <v>/klɜːrk/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>职员</v>
       </c>
-      <c r="D2" t="str">
-        <v>clerk(职员)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>oil</v>
       </c>
       <c r="B3" t="str">
-        <v>oil</v>
+        <v>/ɔɪl/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>石油</v>
       </c>
-      <c r="D3" t="str">
-        <v>oil(石油)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>organization</v>
       </c>
       <c r="B4" t="str">
-        <v>organization</v>
+        <v>/ˌɔːrɡənəˈzeɪʃn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>组织</v>
       </c>
-      <c r="D4" t="str">
-        <v>organization(组织)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>tonight</v>
       </c>
       <c r="B5" t="str">
-        <v>tonight</v>
+        <v>/təˈnaɪt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>今晚</v>
       </c>
-      <c r="D5" t="str">
-        <v>tonight(今晚)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>America</v>
       </c>
       <c r="B6" t="str">
-        <v>America</v>
+        <v>/əˈmerɪkə/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>美国</v>
       </c>
-      <c r="D6" t="str">
-        <v>America(美国)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>smile</v>
       </c>
       <c r="B7" t="str">
-        <v>smile</v>
+        <v>/smaɪl/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D7" t="str">
         <v>微笑</v>
       </c>
-      <c r="D7" t="str">
-        <v>smile(微笑)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>leader</v>
       </c>
       <c r="B8" t="str">
-        <v>leader</v>
+        <v>/ˈliːdər/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>领导者</v>
       </c>
-      <c r="D8" t="str">
-        <v>leader(领导者)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>transfer</v>
       </c>
       <c r="B9" t="str">
-        <v>transfer</v>
+        <v>/trænsˈfɜːr/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>调任</v>
       </c>
-      <c r="D9" t="str">
-        <v>transfer(调任)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>appoint</v>
       </c>
       <c r="B10" t="str">
-        <v>clerk</v>
+        <v>/əˈpɔɪnt/</v>
       </c>
       <c r="C10" t="str">
-        <v>职员</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D10" t="str">
-        <v>clerk(职员)📢</v>
+        <v>任命</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>resume</v>
       </c>
       <c r="B11" t="str">
-        <v>appoint</v>
+        <v>/rɪˈzuːm/</v>
       </c>
       <c r="C11" t="str">
-        <v>任命</v>
+        <v>n./vt.</v>
       </c>
       <c r="D11" t="str">
-        <v>appoint(任命)📢</v>
+        <v>简历</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>record</v>
       </c>
       <c r="B12" t="str">
-        <v>resume</v>
+        <v>/ˈrekərd; rɪˈkɔːrd/</v>
       </c>
       <c r="C12" t="str">
-        <v>简历</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D12" t="str">
-        <v>resume(简历)📢</v>
+        <v>记录</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>quiet</v>
       </c>
       <c r="B13" t="str">
-        <v>record</v>
+        <v>/ˈkwaɪət/</v>
       </c>
       <c r="C13" t="str">
-        <v>记录</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D13" t="str">
-        <v>record(记录)📢</v>
+        <v>安静的</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>many</v>
       </c>
       <c r="B14" t="str">
-        <v>quiet</v>
+        <v>/ˈmeni/</v>
       </c>
       <c r="C14" t="str">
-        <v>安静的</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D14" t="str">
-        <v>quiet(安静的)📢</v>
+        <v>许多</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>division</v>
       </c>
       <c r="B15" t="str">
-        <v>many</v>
+        <v>/dɪˈvɪʒn/</v>
       </c>
       <c r="C15" t="str">
-        <v>许多</v>
+        <v>n.</v>
       </c>
       <c r="D15" t="str">
-        <v>many(许多)📢</v>
+        <v>部门</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>ultimate</v>
       </c>
       <c r="B16" t="str">
-        <v>division</v>
+        <v>/ˈʌltɪmət/</v>
       </c>
       <c r="C16" t="str">
-        <v>部门</v>
+        <v>n./adj.</v>
       </c>
       <c r="D16" t="str">
-        <v>division(部门)📢</v>
+        <v>最终的</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>plane</v>
       </c>
       <c r="B17" t="str">
-        <v>ultimate</v>
+        <v>/pleɪn/</v>
       </c>
       <c r="C17" t="str">
-        <v>最终的</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D17" t="str">
-        <v>ultimate(最终的)📢</v>
+        <v>飞机</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>manly</v>
       </c>
       <c r="B18" t="str">
-        <v>plane</v>
+        <v>/ˈmænli/</v>
       </c>
       <c r="C18" t="str">
-        <v>飞机</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D18" t="str">
-        <v>plane(飞机)📢</v>
+        <v>男子气概的</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>secondary</v>
       </c>
       <c r="B19" t="str">
-        <v>quiet</v>
+        <v>/ˈsekənderi/</v>
       </c>
       <c r="C19" t="str">
-        <v>安静</v>
+        <v>n./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>quiet(安静)📢</v>
+        <v>次要的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>zealous</v>
       </c>
       <c r="B20" t="str">
-        <v>manly</v>
+        <v>/ˈzeləs/</v>
       </c>
       <c r="C20" t="str">
-        <v>男子气概的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>manly(男子气概的)📢</v>
+        <v>热心的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>symbol</v>
       </c>
       <c r="B21" t="str">
-        <v>secondary</v>
+        <v>/ˈsɪmbl/</v>
       </c>
       <c r="C21" t="str">
-        <v>次要的</v>
+        <v>n.</v>
       </c>
       <c r="D21" t="str">
-        <v>secondary(次要的)📢</v>
+        <v>象征</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>cheerful</v>
       </c>
       <c r="B22" t="str">
-        <v>zealous</v>
+        <v>/ˈtʃɪrfl/</v>
       </c>
       <c r="C22" t="str">
-        <v>热心的</v>
+        <v>adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>zealous(热心的)📢</v>
+        <v>快乐的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>pool</v>
       </c>
       <c r="B23" t="str">
-        <v>symbol</v>
+        <v>/puːl/</v>
       </c>
       <c r="C23" t="str">
-        <v>象征</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D23" t="str">
-        <v>symbol(象征)📢</v>
+        <v>池塘</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>indirect</v>
       </c>
       <c r="B24" t="str">
-        <v>leader</v>
+        <v>/ˌɪndəˈrekt/</v>
       </c>
       <c r="C24" t="str">
-        <v>领导者</v>
+        <v>adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>leader(领导者)📢</v>
+        <v>间接的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>instinct</v>
       </c>
       <c r="B25" t="str">
-        <v>cheerful</v>
+        <v>/ˈɪnstɪŋkt/</v>
       </c>
       <c r="C25" t="str">
-        <v>快乐的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>cheerful(快乐的)📢</v>
+        <v>直觉</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>attract</v>
       </c>
       <c r="B26" t="str">
-        <v>pool</v>
+        <v>/əˈtrækt/</v>
       </c>
       <c r="C26" t="str">
-        <v>池塘</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>pool(池塘)📢</v>
+        <v>吸引</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>separate</v>
       </c>
       <c r="B27" t="str">
-        <v>indirect</v>
+        <v>/ˈseprət/</v>
       </c>
       <c r="C27" t="str">
-        <v>间接的</v>
+        <v>v./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>indirect(间接的)📢</v>
+        <v>分开的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>only</v>
       </c>
       <c r="B28" t="str">
-        <v>instinct</v>
+        <v>/ˈoʊnli/</v>
       </c>
       <c r="C28" t="str">
-        <v>直觉</v>
+        <v>v./adj./adv./conj.</v>
       </c>
       <c r="D28" t="str">
-        <v>instinct(直觉)📢</v>
+        <v>仅仅</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>encourage</v>
       </c>
       <c r="B29" t="str">
-        <v>attract</v>
+        <v>/ɪnˈkɜːrɪdʒ/</v>
       </c>
       <c r="C29" t="str">
-        <v>吸引</v>
+        <v>vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>attract(吸引)📢</v>
+        <v>鼓励</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>brother</v>
       </c>
       <c r="B30" t="str">
-        <v>smile</v>
+        <v>/ˈbrʌðər/</v>
       </c>
       <c r="C30" t="str">
-        <v>微笑</v>
+        <v>n./int.</v>
       </c>
       <c r="D30" t="str">
-        <v>smile(微笑)📢</v>
+        <v>兄弟</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>fatal</v>
       </c>
       <c r="B31" t="str">
-        <v>separate</v>
+        <v>/ˈfeɪtl/</v>
       </c>
       <c r="C31" t="str">
-        <v>分开的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>separate(分开的)📢</v>
+        <v>致命的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>culture</v>
       </c>
       <c r="B32" t="str">
-        <v>only</v>
+        <v>/ˈkʌltʃər/</v>
       </c>
       <c r="C32" t="str">
-        <v>仅仅</v>
+        <v>n./vt.</v>
       </c>
       <c r="D32" t="str">
-        <v>only(仅仅)📢</v>
+        <v>文化</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>wreath</v>
       </c>
       <c r="B33" t="str">
-        <v>encourage</v>
+        <v>/riːθ/</v>
       </c>
       <c r="C33" t="str">
-        <v>鼓励</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>encourage(鼓励)📢</v>
+        <v>花冠</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>daylight</v>
       </c>
       <c r="B34" t="str">
-        <v>brother</v>
+        <v>/ˈdeɪlaɪt/</v>
       </c>
       <c r="C34" t="str">
-        <v>兄弟</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>brother(兄弟)📢</v>
+        <v>日光</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>preference</v>
       </c>
       <c r="B35" t="str">
-        <v>fatal</v>
+        <v>/ˈprefrəns/</v>
       </c>
       <c r="C35" t="str">
-        <v>致命的</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>fatal(致命的)📢</v>
+        <v>偏爱</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>identical</v>
       </c>
       <c r="B36" t="str">
-        <v>culture</v>
+        <v>/aɪˈdentɪkl/</v>
       </c>
       <c r="C36" t="str">
-        <v>文化</v>
+        <v>n./adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>culture(文化)📢</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>wreath</v>
-      </c>
-      <c r="C37" t="str">
-        <v>花冠</v>
-      </c>
-      <c r="D37" t="str">
-        <v>wreath(花冠)📢</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>daylight</v>
-      </c>
-      <c r="C38" t="str">
-        <v>日光</v>
-      </c>
-      <c r="D38" t="str">
-        <v>daylight(日光)📢</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>preference</v>
-      </c>
-      <c r="C39" t="str">
-        <v>偏爱</v>
-      </c>
-      <c r="D39" t="str">
-        <v>preference(偏爱)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>identical</v>
-      </c>
-      <c r="C40" t="str">
         <v>完全相同的</v>
-      </c>
-      <c r="D40" t="str">
-        <v>identical(完全相同的)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>transfer</v>
-      </c>
-      <c r="C41" t="str">
-        <v>转移</v>
-      </c>
-      <c r="D41" t="str">
-        <v>transfer(转移)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
   </ignoredErrors>
 </worksheet>
 </file>